--- a/eoptolink/dist/20261025_新易盛模型_v0.1.xlsx
+++ b/eoptolink/dist/20261025_新易盛模型_v0.1.xlsx
@@ -3727,7 +3727,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">innolight/dist/20261024_</t>
+      <t xml:space="preserve">innolight/dist/20261025_</t>
     </r>
     <r>
       <rPr>
@@ -3746,7 +3746,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.1.xlsx</t>
+      <t xml:space="preserve">_v0.1.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4034,7 +4034,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">innolight/dist/20261024_</t>
+      <t xml:space="preserve">innolight/dist/20261025_</t>
     </r>
     <r>
       <rPr>
@@ -4053,7 +4053,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.1.xlsx</t>
+      <t xml:space="preserve">_v0.1.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4201,7 +4201,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261023_</t>
+      <t xml:space="preserve">tsmc/dist/20261025_</t>
     </r>
     <r>
       <rPr>
@@ -4220,7 +4220,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4438,7 +4438,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261023_</t>
+      <t xml:space="preserve">tsmc/dist/20261025_</t>
     </r>
     <r>
       <rPr>
@@ -4457,7 +4457,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4559,7 +4559,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261023_</t>
+      <t xml:space="preserve">tsmc/dist/20261025_</t>
     </r>
     <r>
       <rPr>
@@ -4578,7 +4578,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4680,7 +4680,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261023_</t>
+      <t xml:space="preserve">tsmc/dist/20261025_</t>
     </r>
     <r>
       <rPr>
@@ -4699,7 +4699,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4801,7 +4801,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261023_</t>
+      <t xml:space="preserve">tsmc/dist/20261025_</t>
     </r>
     <r>
       <rPr>
@@ -4820,7 +4820,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4922,7 +4922,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261023_</t>
+      <t xml:space="preserve">tsmc/dist/20261025_</t>
     </r>
     <r>
       <rPr>
@@ -4941,7 +4941,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
